--- a/artfynd/A 50453-2025 artfynd.xlsx
+++ b/artfynd/A 50453-2025 artfynd.xlsx
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>

--- a/artfynd/A 50453-2025 artfynd.xlsx
+++ b/artfynd/A 50453-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1939206</v>
+        <v>133168</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bastuhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469459.1602551297</v>
+        <v>469346</v>
       </c>
       <c r="R2" t="n">
-        <v>6654946.693734673</v>
+        <v>6654817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +752,14 @@
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>bålar á 1 cm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +773,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Triviallövskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -784,7 +783,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>sten</t>
+          <t>grovt träd</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133168</v>
+        <v>375873</v>
       </c>
       <c r="B3" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,31 +812,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>392</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469345.9402201959</v>
+        <v>469548</v>
       </c>
       <c r="R3" t="n">
-        <v>6654816.689257021</v>
+        <v>6654811</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,26 +878,11 @@
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>bålar á 1 cm2</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -915,17 +894,17 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Triviallövskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>igenväxande hagmark</t>
+          <t>ladruin i granplanterad hagmark</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>grovt träd</t>
+          <t>murket timmer</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,50 +922,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1612157</v>
+        <v>376054</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bastuhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469547.6501194375</v>
+        <v>469327</v>
       </c>
       <c r="R4" t="n">
-        <v>6654811.018780787</v>
+        <v>6654760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,21 +999,11 @@
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1042,12 +1015,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Triviallövskog</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>ladruin i granplanterad hagmark</t>
+          <t>ladruin i igenväxande hagmark</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1070,15 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1909276</v>
+        <v>1612157</v>
       </c>
       <c r="B5" t="n">
-        <v>76862</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,43 +1054,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6443</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bastuhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469547.6501194375</v>
+        <v>469548</v>
       </c>
       <c r="R5" t="n">
-        <v>6654811.018780787</v>
+        <v>6654811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,24 +1111,9 @@
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-05-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 bålar á 4 cm2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1211,47 +1155,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>375873</v>
+        <v>1909276</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>6443</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1260,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469547.6501194375</v>
+        <v>469548</v>
       </c>
       <c r="R6" t="n">
-        <v>6654811.018780787</v>
+        <v>6654811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1293,19 +1232,14 @@
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 bålar á 4 cm2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,47 +1281,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>376054</v>
+        <v>1899651</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1396,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469327.4485561497</v>
+        <v>469576</v>
       </c>
       <c r="R7" t="n">
-        <v>6654760.36562985</v>
+        <v>6654768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,21 +1358,11 @@
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1453,19 +1372,14 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Triviallövskog</t>
-        </is>
-      </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>ladruin i igenväxande hagmark</t>
+          <t>övergiven gård</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>murket timmer</t>
+          <t>grovt träd</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1483,15 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2027672</v>
+        <v>1899653</v>
       </c>
       <c r="B8" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,21 +1408,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1523,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469453.078678028</v>
+        <v>469584</v>
       </c>
       <c r="R8" t="n">
-        <v>6654937.748104414</v>
+        <v>6654766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1556,48 +1465,23 @@
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>kan vara Nephroma helveticum</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>igenväxande hagmark</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>gammalt träd</t>
+          <t>övergiven gård</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1615,15 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1939207</v>
+        <v>1907185</v>
       </c>
       <c r="B9" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,34 +1510,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bastuhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469453.078678028</v>
+        <v>469584</v>
       </c>
       <c r="R9" t="n">
-        <v>6654937.748104414</v>
+        <v>6654766</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1688,21 +1576,11 @@
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2013-05-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1712,19 +1590,9 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>igenväxande hagmark</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>gammalt träd</t>
+          <t>övergiven gård</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1739,6 +1607,449 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1939206</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bastuhöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>469459</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6654947</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>igenväxande hagmark</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>sten</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1939207</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bastuhöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>469453</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6654938</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>igenväxande hagmark</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>gammalt träd</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1939209</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bastuhöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>469584</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6654766</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>övergiven gård</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2027672</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bastuhöjden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>469453</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6654938</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säfsnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>kan vara Nephroma helveticum</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>igenväxande hagmark</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>gammalt träd</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
